--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118505053</v>
+        <v>118504980</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,42 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562234</v>
+        <v>562368</v>
       </c>
       <c r="R4" t="n">
-        <v>6923977</v>
+        <v>6923765</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504980</v>
+        <v>118505073</v>
       </c>
       <c r="B5" t="n">
-        <v>90788</v>
+        <v>5166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562368</v>
+        <v>562039</v>
       </c>
       <c r="R5" t="n">
-        <v>6923765</v>
+        <v>6924264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118505073</v>
+        <v>118505053</v>
       </c>
       <c r="B6" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1095,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562039</v>
+        <v>562234</v>
       </c>
       <c r="R6" t="n">
-        <v>6924264</v>
+        <v>6923977</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118505007</v>
+        <v>118504940</v>
       </c>
       <c r="B18" t="n">
-        <v>79565</v>
+        <v>100017</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,25 +2335,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561968</v>
+        <v>562089</v>
       </c>
       <c r="R18" t="n">
-        <v>6924394</v>
+        <v>6924198</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,6 +2407,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2425,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118504940</v>
+        <v>118505007</v>
       </c>
       <c r="B19" t="n">
-        <v>100017</v>
+        <v>79565</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2437,25 +2438,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2465,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562089</v>
+        <v>561968</v>
       </c>
       <c r="R19" t="n">
-        <v>6924198</v>
+        <v>6924394</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,7 +2510,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118504969</v>
+        <v>118505056</v>
       </c>
       <c r="B24" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,38 +2969,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562082</v>
+        <v>562375</v>
       </c>
       <c r="R24" t="n">
-        <v>6924209</v>
+        <v>6923803</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118505048</v>
+        <v>118504969</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3071,42 +3075,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562281</v>
+        <v>562082</v>
       </c>
       <c r="R25" t="n">
-        <v>6923926</v>
+        <v>6924209</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118505056</v>
+        <v>118505048</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562375</v>
+        <v>562281</v>
       </c>
       <c r="R26" t="n">
-        <v>6923803</v>
+        <v>6923926</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -2957,10 +2957,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118505056</v>
+        <v>118504969</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,42 +2969,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562375</v>
+        <v>562082</v>
       </c>
       <c r="R24" t="n">
-        <v>6923803</v>
+        <v>6924209</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,10 +3059,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118504969</v>
+        <v>118505048</v>
       </c>
       <c r="B25" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3075,38 +3071,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562082</v>
+        <v>562281</v>
       </c>
       <c r="R25" t="n">
-        <v>6924209</v>
+        <v>6923926</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118505048</v>
+        <v>118505056</v>
       </c>
       <c r="B26" t="n">
         <v>97846</v>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562281</v>
+        <v>562375</v>
       </c>
       <c r="R26" t="n">
-        <v>6923926</v>
+        <v>6923803</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504943</v>
+        <v>118504977</v>
       </c>
       <c r="B2" t="n">
-        <v>57443</v>
+        <v>90947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562348</v>
+        <v>562237</v>
       </c>
       <c r="R2" t="n">
-        <v>6923831</v>
+        <v>6923990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118505065</v>
+        <v>118504930</v>
       </c>
       <c r="B3" t="n">
-        <v>90518</v>
+        <v>101010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562225</v>
+        <v>561956</v>
       </c>
       <c r="R3" t="n">
-        <v>6923974</v>
+        <v>6924377</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504980</v>
+        <v>118504984</v>
       </c>
       <c r="B4" t="n">
-        <v>90788</v>
+        <v>96801</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562368</v>
+        <v>562380</v>
       </c>
       <c r="R4" t="n">
-        <v>6923765</v>
+        <v>6923643</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118505073</v>
+        <v>118504983</v>
       </c>
       <c r="B5" t="n">
-        <v>5166</v>
+        <v>90788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562039</v>
+        <v>562033</v>
       </c>
       <c r="R5" t="n">
-        <v>6924264</v>
+        <v>6924263</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118505053</v>
+        <v>118504982</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,42 +1099,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562234</v>
+        <v>562061</v>
       </c>
       <c r="R6" t="n">
-        <v>6923977</v>
+        <v>6924234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1189,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118504930</v>
+        <v>118504932</v>
       </c>
       <c r="B7" t="n">
         <v>101010</v>
@@ -1222,21 +1222,17 @@
           <t>(L.) Bernh.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561956</v>
+        <v>562101</v>
       </c>
       <c r="R7" t="n">
-        <v>6924377</v>
+        <v>6924169</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504977</v>
+        <v>118505053</v>
       </c>
       <c r="B8" t="n">
-        <v>90947</v>
+        <v>97846</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,34 +1307,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562237</v>
+        <v>562234</v>
       </c>
       <c r="R8" t="n">
-        <v>6923990</v>
+        <v>6923977</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118505005</v>
+        <v>118505006</v>
       </c>
       <c r="B9" t="n">
         <v>79565</v>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562354</v>
+        <v>561962</v>
       </c>
       <c r="R9" t="n">
-        <v>6923795</v>
+        <v>6924378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118504984</v>
+        <v>118505060</v>
       </c>
       <c r="B10" t="n">
-        <v>96801</v>
+        <v>97846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1511,38 +1511,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562380</v>
+        <v>561986</v>
       </c>
       <c r="R10" t="n">
-        <v>6923643</v>
+        <v>6924357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,10 +1605,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118504979</v>
+        <v>118505055</v>
       </c>
       <c r="B11" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1613,38 +1617,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562312</v>
+        <v>562159</v>
       </c>
       <c r="R11" t="n">
-        <v>6923893</v>
+        <v>6924104</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118505060</v>
+        <v>118505061</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1738,19 +1746,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561986</v>
+        <v>562347</v>
       </c>
       <c r="R12" t="n">
-        <v>6924357</v>
+        <v>6923798</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,6 +1807,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118505006</v>
+        <v>118504940</v>
       </c>
       <c r="B13" t="n">
-        <v>79565</v>
+        <v>100017</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1821,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1849,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561962</v>
+        <v>562089</v>
       </c>
       <c r="R13" t="n">
-        <v>6924378</v>
+        <v>6924198</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,6 +1910,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1911,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504982</v>
+        <v>118504943</v>
       </c>
       <c r="B14" t="n">
-        <v>90788</v>
+        <v>57443</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562061</v>
+        <v>562348</v>
       </c>
       <c r="R14" t="n">
-        <v>6924234</v>
+        <v>6923831</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2013,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504976</v>
+        <v>118504941</v>
       </c>
       <c r="B15" t="n">
-        <v>90947</v>
+        <v>103349</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2025,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2053,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562243</v>
+        <v>562035</v>
       </c>
       <c r="R15" t="n">
-        <v>6923995</v>
+        <v>6924269</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118505050</v>
+        <v>118504981</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>90788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2127,42 +2145,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562209</v>
+        <v>562239</v>
       </c>
       <c r="R16" t="n">
-        <v>6924009</v>
+        <v>6923998</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118504941</v>
+        <v>118504979</v>
       </c>
       <c r="B17" t="n">
-        <v>103349</v>
+        <v>90788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2233,25 +2247,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2261,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562035</v>
+        <v>562312</v>
       </c>
       <c r="R17" t="n">
-        <v>6924269</v>
+        <v>6923893</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118504940</v>
+        <v>118504980</v>
       </c>
       <c r="B18" t="n">
-        <v>100017</v>
+        <v>90788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2335,25 +2349,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2363,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562089</v>
+        <v>562368</v>
       </c>
       <c r="R18" t="n">
-        <v>6924198</v>
+        <v>6923765</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2407,7 +2421,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2426,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118505007</v>
+        <v>118505056</v>
       </c>
       <c r="B19" t="n">
-        <v>79565</v>
+        <v>97846</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2438,38 +2451,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561968</v>
+        <v>562375</v>
       </c>
       <c r="R19" t="n">
-        <v>6924394</v>
+        <v>6923803</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118505061</v>
+        <v>118505048</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2563,27 +2580,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562347</v>
+        <v>562281</v>
       </c>
       <c r="R20" t="n">
-        <v>6923798</v>
+        <v>6923926</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2624,7 +2633,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2643,7 +2651,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118505055</v>
+        <v>118505050</v>
       </c>
       <c r="B21" t="n">
         <v>97846</v>
@@ -2678,7 +2686,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2687,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562159</v>
+        <v>562209</v>
       </c>
       <c r="R21" t="n">
-        <v>6924104</v>
+        <v>6924009</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118504981</v>
+        <v>118505073</v>
       </c>
       <c r="B22" t="n">
-        <v>90788</v>
+        <v>5166</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,25 +2769,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2789,10 +2797,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562239</v>
+        <v>562039</v>
       </c>
       <c r="R22" t="n">
-        <v>6923998</v>
+        <v>6924264</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,10 +2859,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118505052</v>
+        <v>118504969</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,42 +2871,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562223</v>
+        <v>562082</v>
       </c>
       <c r="R23" t="n">
-        <v>6923970</v>
+        <v>6924209</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2957,10 +2961,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118504969</v>
+        <v>118505058</v>
       </c>
       <c r="B24" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,38 +2973,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562082</v>
+        <v>561975</v>
       </c>
       <c r="R24" t="n">
-        <v>6924209</v>
+        <v>6924380</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3059,10 +3067,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118505048</v>
+        <v>118504976</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>90947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3075,38 +3083,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562281</v>
+        <v>562243</v>
       </c>
       <c r="R25" t="n">
-        <v>6923926</v>
+        <v>6923995</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3165,10 +3169,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118505056</v>
+        <v>118505005</v>
       </c>
       <c r="B26" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3177,42 +3181,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562375</v>
+        <v>562354</v>
       </c>
       <c r="R26" t="n">
-        <v>6923803</v>
+        <v>6923795</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118504983</v>
+        <v>118505007</v>
       </c>
       <c r="B27" t="n">
-        <v>90788</v>
+        <v>79565</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562033</v>
+        <v>561968</v>
       </c>
       <c r="R27" t="n">
-        <v>6924263</v>
+        <v>6924394</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118504932</v>
+        <v>118505052</v>
       </c>
       <c r="B29" t="n">
-        <v>101010</v>
+        <v>97846</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3487,38 +3487,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562101</v>
+        <v>562223</v>
       </c>
       <c r="R29" t="n">
-        <v>6924169</v>
+        <v>6923970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3577,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118505058</v>
+        <v>118505065</v>
       </c>
       <c r="B30" t="n">
-        <v>97846</v>
+        <v>90518</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3589,42 +3593,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561975</v>
+        <v>562225</v>
       </c>
       <c r="R30" t="n">
-        <v>6924380</v>
+        <v>6923974</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504977</v>
+        <v>118504930</v>
       </c>
       <c r="B2" t="n">
-        <v>90947</v>
+        <v>101010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562237</v>
+        <v>561956</v>
       </c>
       <c r="R2" t="n">
-        <v>6923990</v>
+        <v>6924377</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504930</v>
+        <v>118504977</v>
       </c>
       <c r="B3" t="n">
-        <v>101010</v>
+        <v>90947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561956</v>
+        <v>562237</v>
       </c>
       <c r="R3" t="n">
-        <v>6924377</v>
+        <v>6923990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504930</v>
+        <v>118504941</v>
       </c>
       <c r="B2" t="n">
-        <v>101010</v>
+        <v>103349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561956</v>
+        <v>562035</v>
       </c>
       <c r="R2" t="n">
-        <v>6924377</v>
+        <v>6924269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504977</v>
+        <v>118504983</v>
       </c>
       <c r="B3" t="n">
-        <v>90947</v>
+        <v>90788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562237</v>
+        <v>562033</v>
       </c>
       <c r="R3" t="n">
-        <v>6923990</v>
+        <v>6924263</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504984</v>
+        <v>118505056</v>
       </c>
       <c r="B4" t="n">
-        <v>96801</v>
+        <v>97846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562380</v>
+        <v>562375</v>
       </c>
       <c r="R4" t="n">
-        <v>6923643</v>
+        <v>6923803</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504983</v>
+        <v>118505050</v>
       </c>
       <c r="B5" t="n">
-        <v>90788</v>
+        <v>97846</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +997,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562033</v>
+        <v>562209</v>
       </c>
       <c r="R5" t="n">
-        <v>6924263</v>
+        <v>6924009</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504982</v>
+        <v>118505005</v>
       </c>
       <c r="B6" t="n">
-        <v>90788</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,21 +1107,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562061</v>
+        <v>562354</v>
       </c>
       <c r="R6" t="n">
-        <v>6924234</v>
+        <v>6923795</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118504932</v>
+        <v>118505052</v>
       </c>
       <c r="B7" t="n">
-        <v>101010</v>
+        <v>97846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,38 +1205,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562101</v>
+        <v>562223</v>
       </c>
       <c r="R7" t="n">
-        <v>6924169</v>
+        <v>6923970</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,10 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118505053</v>
+        <v>118504969</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,42 +1311,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562234</v>
+        <v>562082</v>
       </c>
       <c r="R8" t="n">
-        <v>6923977</v>
+        <v>6924209</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,7 +1401,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118505006</v>
+        <v>118505007</v>
       </c>
       <c r="B9" t="n">
         <v>79565</v>
@@ -1437,10 +1441,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561962</v>
+        <v>561968</v>
       </c>
       <c r="R9" t="n">
-        <v>6924378</v>
+        <v>6924394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1503,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118505060</v>
+        <v>118505058</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1543,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561986</v>
+        <v>561975</v>
       </c>
       <c r="R10" t="n">
-        <v>6924357</v>
+        <v>6924380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1711,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118505061</v>
+        <v>118505006</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>79565</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1723,50 +1727,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562347</v>
+        <v>561962</v>
       </c>
       <c r="R12" t="n">
-        <v>6923798</v>
+        <v>6924378</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1799,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1826,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504940</v>
+        <v>118504932</v>
       </c>
       <c r="B13" t="n">
-        <v>100017</v>
+        <v>101010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562089</v>
+        <v>562101</v>
       </c>
       <c r="R13" t="n">
-        <v>6924198</v>
+        <v>6924169</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,7 +1901,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1929,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504943</v>
+        <v>118504930</v>
       </c>
       <c r="B14" t="n">
-        <v>57443</v>
+        <v>101010</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,38 +1931,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562348</v>
+        <v>561956</v>
       </c>
       <c r="R14" t="n">
-        <v>6923831</v>
+        <v>6924377</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2031,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504941</v>
+        <v>118504980</v>
       </c>
       <c r="B15" t="n">
-        <v>103349</v>
+        <v>90788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2037,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562035</v>
+        <v>562368</v>
       </c>
       <c r="R15" t="n">
-        <v>6924269</v>
+        <v>6923765</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118504981</v>
+        <v>118505065</v>
       </c>
       <c r="B16" t="n">
-        <v>90788</v>
+        <v>90518</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2143,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562239</v>
+        <v>562225</v>
       </c>
       <c r="R16" t="n">
-        <v>6923998</v>
+        <v>6923974</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2229,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118504979</v>
+        <v>118504982</v>
       </c>
       <c r="B17" t="n">
         <v>90788</v>
@@ -2275,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562312</v>
+        <v>562061</v>
       </c>
       <c r="R17" t="n">
-        <v>6923893</v>
+        <v>6924234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,7 +2331,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118504980</v>
+        <v>118504979</v>
       </c>
       <c r="B18" t="n">
         <v>90788</v>
@@ -2377,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562368</v>
+        <v>562312</v>
       </c>
       <c r="R18" t="n">
-        <v>6923765</v>
+        <v>6923893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118505056</v>
+        <v>118504970</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,42 +2445,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562375</v>
+        <v>562039</v>
       </c>
       <c r="R19" t="n">
-        <v>6923803</v>
+        <v>6924264</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,7 +2535,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118505048</v>
+        <v>118505061</v>
       </c>
       <c r="B20" t="n">
         <v>97846</v>
@@ -2580,19 +2570,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562281</v>
+        <v>562347</v>
       </c>
       <c r="R20" t="n">
-        <v>6923926</v>
+        <v>6923798</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,6 +2631,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2651,10 +2650,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118505050</v>
+        <v>118504976</v>
       </c>
       <c r="B21" t="n">
-        <v>97846</v>
+        <v>90947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,38 +2666,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562209</v>
+        <v>562243</v>
       </c>
       <c r="R21" t="n">
-        <v>6924009</v>
+        <v>6923995</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2757,10 +2752,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118505073</v>
+        <v>118505048</v>
       </c>
       <c r="B22" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2769,38 +2764,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562039</v>
+        <v>562281</v>
       </c>
       <c r="R22" t="n">
-        <v>6924264</v>
+        <v>6923926</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,10 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118504969</v>
+        <v>118504943</v>
       </c>
       <c r="B23" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,21 +2874,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2899,10 +2898,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562082</v>
+        <v>562348</v>
       </c>
       <c r="R23" t="n">
-        <v>6924209</v>
+        <v>6923831</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2961,10 +2960,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118505058</v>
+        <v>118504940</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>100017</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2973,42 +2972,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222771</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561975</v>
+        <v>562089</v>
       </c>
       <c r="R24" t="n">
-        <v>6924380</v>
+        <v>6924198</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3049,6 +3044,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3067,10 +3063,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118504976</v>
+        <v>118505060</v>
       </c>
       <c r="B25" t="n">
-        <v>90947</v>
+        <v>97846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,34 +3079,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562243</v>
+        <v>561986</v>
       </c>
       <c r="R25" t="n">
-        <v>6923995</v>
+        <v>6924357</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,10 +3169,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118505005</v>
+        <v>118504977</v>
       </c>
       <c r="B26" t="n">
-        <v>79565</v>
+        <v>90947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562354</v>
+        <v>562237</v>
       </c>
       <c r="R26" t="n">
-        <v>6923795</v>
+        <v>6923990</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118505007</v>
+        <v>118504981</v>
       </c>
       <c r="B27" t="n">
-        <v>79565</v>
+        <v>90788</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561968</v>
+        <v>562239</v>
       </c>
       <c r="R27" t="n">
-        <v>6924394</v>
+        <v>6923998</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118504970</v>
+        <v>118505073</v>
       </c>
       <c r="B28" t="n">
-        <v>57306</v>
+        <v>5166</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3385,25 +3385,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118505052</v>
+        <v>118505053</v>
       </c>
       <c r="B29" t="n">
         <v>97846</v>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562223</v>
+        <v>562234</v>
       </c>
       <c r="R29" t="n">
-        <v>6923970</v>
+        <v>6923977</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118505065</v>
+        <v>118504984</v>
       </c>
       <c r="B30" t="n">
-        <v>90518</v>
+        <v>96801</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,25 +3593,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562225</v>
+        <v>562380</v>
       </c>
       <c r="R30" t="n">
-        <v>6923974</v>
+        <v>6923643</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504941</v>
+        <v>118504932</v>
       </c>
       <c r="B2" t="n">
-        <v>103349</v>
+        <v>101017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562035</v>
+        <v>562101</v>
       </c>
       <c r="R2" t="n">
-        <v>6924269</v>
+        <v>6924169</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504983</v>
+        <v>118505058</v>
       </c>
       <c r="B3" t="n">
-        <v>90788</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562033</v>
+        <v>561975</v>
       </c>
       <c r="R3" t="n">
-        <v>6924263</v>
+        <v>6924380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118505056</v>
+        <v>118504976</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>90954</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,38 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562375</v>
+        <v>562243</v>
       </c>
       <c r="R4" t="n">
-        <v>6923803</v>
+        <v>6923995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118505050</v>
+        <v>118504981</v>
       </c>
       <c r="B5" t="n">
-        <v>97846</v>
+        <v>90795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +997,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562209</v>
+        <v>562239</v>
       </c>
       <c r="R5" t="n">
-        <v>6924009</v>
+        <v>6923998</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118505005</v>
+        <v>118504980</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>90795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562354</v>
+        <v>562368</v>
       </c>
       <c r="R6" t="n">
-        <v>6923795</v>
+        <v>6923765</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118505052</v>
+        <v>118505061</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1228,19 +1224,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562223</v>
+        <v>562347</v>
       </c>
       <c r="R7" t="n">
-        <v>6923970</v>
+        <v>6923798</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1285,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1299,10 +1304,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118504969</v>
+        <v>118505056</v>
       </c>
       <c r="B8" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1311,38 +1316,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562082</v>
+        <v>562375</v>
       </c>
       <c r="R8" t="n">
-        <v>6924209</v>
+        <v>6923803</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,10 +1410,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118505007</v>
+        <v>118504940</v>
       </c>
       <c r="B9" t="n">
-        <v>79565</v>
+        <v>100024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1413,25 +1422,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1441,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561968</v>
+        <v>562089</v>
       </c>
       <c r="R9" t="n">
-        <v>6924394</v>
+        <v>6924198</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1494,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1503,10 +1513,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118505058</v>
+        <v>118504941</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>103356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1515,42 +1525,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561975</v>
+        <v>562035</v>
       </c>
       <c r="R10" t="n">
-        <v>6924380</v>
+        <v>6924269</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1615,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118505055</v>
+        <v>118504982</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>90795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1621,42 +1627,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562159</v>
+        <v>562061</v>
       </c>
       <c r="R11" t="n">
-        <v>6924104</v>
+        <v>6924234</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1717,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118505006</v>
+        <v>118505005</v>
       </c>
       <c r="B12" t="n">
-        <v>79565</v>
+        <v>79572</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1755,10 +1757,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561962</v>
+        <v>562354</v>
       </c>
       <c r="R12" t="n">
-        <v>6924378</v>
+        <v>6923795</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1819,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504932</v>
+        <v>118504983</v>
       </c>
       <c r="B13" t="n">
-        <v>101010</v>
+        <v>90795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1831,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562101</v>
+        <v>562033</v>
       </c>
       <c r="R13" t="n">
-        <v>6924169</v>
+        <v>6924263</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118504930</v>
+        <v>118505048</v>
       </c>
       <c r="B14" t="n">
-        <v>101010</v>
+        <v>97853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,30 +1933,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1963,10 +1965,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561956</v>
+        <v>562281</v>
       </c>
       <c r="R14" t="n">
-        <v>6924377</v>
+        <v>6923926</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504980</v>
+        <v>118504984</v>
       </c>
       <c r="B15" t="n">
-        <v>90788</v>
+        <v>96808</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,25 +2039,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562368</v>
+        <v>562380</v>
       </c>
       <c r="R15" t="n">
-        <v>6923765</v>
+        <v>6923643</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118505065</v>
+        <v>118504970</v>
       </c>
       <c r="B16" t="n">
-        <v>90518</v>
+        <v>57306</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,21 +2145,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562225</v>
+        <v>562039</v>
       </c>
       <c r="R16" t="n">
-        <v>6923974</v>
+        <v>6924264</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118504982</v>
+        <v>118505053</v>
       </c>
       <c r="B17" t="n">
-        <v>90788</v>
+        <v>97853</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,38 +2243,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562061</v>
+        <v>562234</v>
       </c>
       <c r="R17" t="n">
-        <v>6924234</v>
+        <v>6923977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118504979</v>
+        <v>118504930</v>
       </c>
       <c r="B18" t="n">
-        <v>90788</v>
+        <v>101017</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2343,38 +2349,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>562312</v>
+        <v>561956</v>
       </c>
       <c r="R18" t="n">
-        <v>6923893</v>
+        <v>6924377</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118504970</v>
+        <v>118505060</v>
       </c>
       <c r="B19" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2445,38 +2455,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>562039</v>
+        <v>561986</v>
       </c>
       <c r="R19" t="n">
-        <v>6924264</v>
+        <v>6924357</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,10 +2549,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118505061</v>
+        <v>118505055</v>
       </c>
       <c r="B20" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2570,27 +2584,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>180</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562347</v>
+        <v>562159</v>
       </c>
       <c r="R20" t="n">
-        <v>6923798</v>
+        <v>6924104</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2637,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2650,10 +2655,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118504976</v>
+        <v>118505065</v>
       </c>
       <c r="B21" t="n">
-        <v>90947</v>
+        <v>90525</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2662,25 +2667,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2690,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>562243</v>
+        <v>562225</v>
       </c>
       <c r="R21" t="n">
-        <v>6923995</v>
+        <v>6923974</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2752,10 +2757,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118505048</v>
+        <v>118505050</v>
       </c>
       <c r="B22" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2787,7 +2792,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2796,10 +2801,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562281</v>
+        <v>562209</v>
       </c>
       <c r="R22" t="n">
-        <v>6923926</v>
+        <v>6924009</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,10 +2965,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118504940</v>
+        <v>118504969</v>
       </c>
       <c r="B24" t="n">
-        <v>100017</v>
+        <v>57306</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2972,25 +2977,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222771</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3000,10 +3005,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562089</v>
+        <v>562082</v>
       </c>
       <c r="R24" t="n">
-        <v>6924198</v>
+        <v>6924209</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3044,7 +3049,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3063,10 +3067,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118505060</v>
+        <v>118504977</v>
       </c>
       <c r="B25" t="n">
-        <v>97846</v>
+        <v>90954</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3079,38 +3083,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561986</v>
+        <v>562237</v>
       </c>
       <c r="R25" t="n">
-        <v>6924357</v>
+        <v>6923990</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3169,10 +3169,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118504977</v>
+        <v>118505073</v>
       </c>
       <c r="B26" t="n">
-        <v>90947</v>
+        <v>5166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562237</v>
+        <v>562039</v>
       </c>
       <c r="R26" t="n">
-        <v>6923990</v>
+        <v>6924264</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118504981</v>
+        <v>118504979</v>
       </c>
       <c r="B27" t="n">
-        <v>90788</v>
+        <v>90795</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562239</v>
+        <v>562312</v>
       </c>
       <c r="R27" t="n">
-        <v>6923998</v>
+        <v>6923893</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118505073</v>
+        <v>118505007</v>
       </c>
       <c r="B28" t="n">
-        <v>5166</v>
+        <v>79572</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3385,25 +3385,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562039</v>
+        <v>561968</v>
       </c>
       <c r="R28" t="n">
-        <v>6924264</v>
+        <v>6924394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118505053</v>
+        <v>118505052</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562234</v>
+        <v>562223</v>
       </c>
       <c r="R29" t="n">
-        <v>6923977</v>
+        <v>6923970</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118504984</v>
+        <v>118505006</v>
       </c>
       <c r="B30" t="n">
-        <v>96801</v>
+        <v>79572</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,25 +3593,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3621,10 +3621,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562380</v>
+        <v>561962</v>
       </c>
       <c r="R30" t="n">
-        <v>6923643</v>
+        <v>6924378</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118504932</v>
+        <v>118505058</v>
       </c>
       <c r="B2" t="n">
-        <v>101017</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562101</v>
+        <v>561975</v>
       </c>
       <c r="R2" t="n">
-        <v>6924169</v>
+        <v>6924380</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118505058</v>
+        <v>118504932</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>101017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561975</v>
+        <v>562101</v>
       </c>
       <c r="R3" t="n">
-        <v>6924380</v>
+        <v>6924169</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118505058</v>
+        <v>118504970</v>
       </c>
       <c r="B2" t="n">
-        <v>97853</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561975</v>
+        <v>562039</v>
       </c>
       <c r="R2" t="n">
-        <v>6924380</v>
+        <v>6924264</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118504932</v>
+        <v>118504943</v>
       </c>
       <c r="B3" t="n">
-        <v>101017</v>
+        <v>57443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562101</v>
+        <v>562348</v>
       </c>
       <c r="R3" t="n">
-        <v>6924169</v>
+        <v>6923831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118504976</v>
+        <v>118504940</v>
       </c>
       <c r="B4" t="n">
-        <v>90954</v>
+        <v>100024</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562243</v>
+        <v>562089</v>
       </c>
       <c r="R4" t="n">
-        <v>6923995</v>
+        <v>6924198</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -985,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118504981</v>
+        <v>118505053</v>
       </c>
       <c r="B5" t="n">
-        <v>90795</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +994,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562239</v>
+        <v>562234</v>
       </c>
       <c r="R5" t="n">
-        <v>6923998</v>
+        <v>6923977</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118504980</v>
+        <v>118505052</v>
       </c>
       <c r="B6" t="n">
-        <v>90795</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1100,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562368</v>
+        <v>562223</v>
       </c>
       <c r="R6" t="n">
-        <v>6923765</v>
+        <v>6923970</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118505061</v>
+        <v>118505056</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1224,27 +1229,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562347</v>
+        <v>562375</v>
       </c>
       <c r="R7" t="n">
-        <v>6923798</v>
+        <v>6923803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1282,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1304,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118505056</v>
+        <v>118504984</v>
       </c>
       <c r="B8" t="n">
-        <v>97853</v>
+        <v>96808</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,42 +1312,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562375</v>
+        <v>562380</v>
       </c>
       <c r="R8" t="n">
-        <v>6923803</v>
+        <v>6923643</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118504940</v>
+        <v>118505048</v>
       </c>
       <c r="B9" t="n">
-        <v>100024</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1422,38 +1414,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562089</v>
+        <v>562281</v>
       </c>
       <c r="R9" t="n">
-        <v>6924198</v>
+        <v>6923926</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1490,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1513,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118504941</v>
+        <v>118505058</v>
       </c>
       <c r="B10" t="n">
-        <v>103356</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,38 +1520,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562035</v>
+        <v>561975</v>
       </c>
       <c r="R10" t="n">
-        <v>6924269</v>
+        <v>6924380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118504982</v>
+        <v>118504930</v>
       </c>
       <c r="B11" t="n">
-        <v>90795</v>
+        <v>101017</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1627,38 +1626,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562061</v>
+        <v>561956</v>
       </c>
       <c r="R11" t="n">
-        <v>6924234</v>
+        <v>6924377</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1819,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118504983</v>
+        <v>118505060</v>
       </c>
       <c r="B13" t="n">
-        <v>90795</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,38 +1834,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562033</v>
+        <v>561986</v>
       </c>
       <c r="R13" t="n">
-        <v>6924263</v>
+        <v>6924357</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1921,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118505048</v>
+        <v>118504982</v>
       </c>
       <c r="B14" t="n">
-        <v>97853</v>
+        <v>90795</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1933,42 +1940,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562281</v>
+        <v>562061</v>
       </c>
       <c r="R14" t="n">
-        <v>6923926</v>
+        <v>6924234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2027,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118504984</v>
+        <v>118504976</v>
       </c>
       <c r="B15" t="n">
-        <v>96808</v>
+        <v>90954</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2039,25 +2042,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2067,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>562380</v>
+        <v>562243</v>
       </c>
       <c r="R15" t="n">
-        <v>6923643</v>
+        <v>6923995</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2129,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118504970</v>
+        <v>118505007</v>
       </c>
       <c r="B16" t="n">
-        <v>57306</v>
+        <v>79572</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,21 +2148,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>562039</v>
+        <v>561968</v>
       </c>
       <c r="R16" t="n">
-        <v>6924264</v>
+        <v>6924394</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118505053</v>
+        <v>118505073</v>
       </c>
       <c r="B17" t="n">
-        <v>97853</v>
+        <v>5166</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2243,42 +2246,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>562234</v>
+        <v>562039</v>
       </c>
       <c r="R17" t="n">
-        <v>6923977</v>
+        <v>6924264</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118504930</v>
+        <v>118504979</v>
       </c>
       <c r="B18" t="n">
-        <v>101017</v>
+        <v>90795</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,42 +2348,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561956</v>
+        <v>562312</v>
       </c>
       <c r="R18" t="n">
-        <v>6924377</v>
+        <v>6923893</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,7 +2438,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118505060</v>
+        <v>118505055</v>
       </c>
       <c r="B19" t="n">
         <v>97853</v>
@@ -2478,7 +2473,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>180</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2487,10 +2482,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561986</v>
+        <v>562159</v>
       </c>
       <c r="R19" t="n">
-        <v>6924357</v>
+        <v>6924104</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,10 +2544,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118505055</v>
+        <v>118504932</v>
       </c>
       <c r="B20" t="n">
-        <v>97853</v>
+        <v>101017</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2561,42 +2556,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>562159</v>
+        <v>562101</v>
       </c>
       <c r="R20" t="n">
-        <v>6924104</v>
+        <v>6924169</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,10 +2748,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118505050</v>
+        <v>118505006</v>
       </c>
       <c r="B22" t="n">
-        <v>97853</v>
+        <v>79572</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2769,42 +2760,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562209</v>
+        <v>561962</v>
       </c>
       <c r="R22" t="n">
-        <v>6924009</v>
+        <v>6924378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2863,10 +2850,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118504943</v>
+        <v>118504941</v>
       </c>
       <c r="B23" t="n">
-        <v>57443</v>
+        <v>103356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2875,25 +2862,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2903,10 +2890,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562348</v>
+        <v>562035</v>
       </c>
       <c r="R23" t="n">
-        <v>6923831</v>
+        <v>6924269</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2965,10 +2952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118504969</v>
+        <v>118504980</v>
       </c>
       <c r="B24" t="n">
-        <v>57306</v>
+        <v>90795</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2981,21 +2968,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3005,10 +2992,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562082</v>
+        <v>562368</v>
       </c>
       <c r="R24" t="n">
-        <v>6924209</v>
+        <v>6923765</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3067,10 +3054,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118504977</v>
+        <v>118505061</v>
       </c>
       <c r="B25" t="n">
-        <v>90954</v>
+        <v>97853</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3083,34 +3070,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562237</v>
+        <v>562347</v>
       </c>
       <c r="R25" t="n">
-        <v>6923990</v>
+        <v>6923798</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3151,6 +3150,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3169,10 +3169,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118505073</v>
+        <v>118504981</v>
       </c>
       <c r="B26" t="n">
-        <v>5166</v>
+        <v>90795</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3181,25 +3181,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562039</v>
+        <v>562239</v>
       </c>
       <c r="R26" t="n">
-        <v>6924264</v>
+        <v>6923998</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,7 +3271,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118504979</v>
+        <v>118504983</v>
       </c>
       <c r="B27" t="n">
         <v>90795</v>
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562312</v>
+        <v>562033</v>
       </c>
       <c r="R27" t="n">
-        <v>6923893</v>
+        <v>6924263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118505007</v>
+        <v>118504969</v>
       </c>
       <c r="B28" t="n">
-        <v>79572</v>
+        <v>57306</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561968</v>
+        <v>562082</v>
       </c>
       <c r="R28" t="n">
-        <v>6924394</v>
+        <v>6924209</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118505052</v>
+        <v>118504977</v>
       </c>
       <c r="B29" t="n">
-        <v>97853</v>
+        <v>90954</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3491,38 +3491,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562223</v>
+        <v>562237</v>
       </c>
       <c r="R29" t="n">
-        <v>6923970</v>
+        <v>6923990</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3581,10 +3577,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118505006</v>
+        <v>118505050</v>
       </c>
       <c r="B30" t="n">
-        <v>79572</v>
+        <v>97853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3593,38 +3589,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Roggån, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561962</v>
+        <v>562209</v>
       </c>
       <c r="R30" t="n">
-        <v>6924378</v>
+        <v>6924009</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -1414,12 +1414,7 @@
         <v>118504970</v>
       </c>
       <c r="B9" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2858,12 +2853,7 @@
         <v>118504969</v>
       </c>
       <c r="B23" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -1414,7 +1414,7 @@
         <v>118504970</v>
       </c>
       <c r="B9" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>118504969</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -1414,7 +1414,7 @@
         <v>118504970</v>
       </c>
       <c r="B9" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>118504969</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -1414,7 +1414,7 @@
         <v>118504970</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>118504969</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -1414,7 +1414,7 @@
         <v>118504970</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>118504969</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -1414,7 +1414,7 @@
         <v>118504970</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>118504969</v>
       </c>
       <c r="B23" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 47789-2023 artfynd.xlsx
+++ b/artfynd/A 47789-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504979</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504981</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504982</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505065</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504976</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504977</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505067</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504944</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505005</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1840,6 +1900,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505006</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1937,6 +2002,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505007</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2034,6 +2104,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504969</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2131,6 +2206,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504970</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2228,6 +2308,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505073</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2325,6 +2410,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504943</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2422,6 +2512,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505032</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505048</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505050</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2725,6 +2830,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505052</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505053</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2927,6 +3042,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505055</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3028,6 +3148,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505056</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3129,6 +3254,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505058</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3230,6 +3360,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505060</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3340,6 +3475,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118505061</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3441,6 +3581,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504930</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3538,6 +3683,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504931</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3635,6 +3785,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504932</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3732,6 +3887,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504984</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3829,6 +3989,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504936</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3926,6 +4091,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504941</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4024,8 +4194,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118504940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>